--- a/docs/Decodifiche/146_dmnm_dec_mezzo_trasporto.xlsx
+++ b/docs/Decodifiche/146_dmnm_dec_mezzo_trasporto.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
   <si>
     <t>ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>A PIEDI (PEDONE, PASSEGGINO, IN BRACCIO)</t>
   </si>
   <si>
-    <t>2025-12-02 20:23:07.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -47,9 +47,6 @@
     <t>SEDIA A ROTELLE</t>
   </si>
   <si>
-    <t>2025-12-02 20:23:08.0</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>CICLOMOTORE</t>
   </si>
   <si>
-    <t>2025-12-02 20:23:09.0</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -119,9 +113,6 @@
     <t>AUTOBUS</t>
   </si>
   <si>
-    <t>2025-12-02 20:23:10.0</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -156,9 +147,6 @@
   </si>
   <si>
     <t>SCONOSCIUTO</t>
-  </si>
-  <si>
-    <t>2025-12-02 20:23:11.0</t>
   </si>
   <si>
     <t>20</t>
@@ -272,7 +260,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -283,291 +271,291 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
